--- a/Models/Птицы/Датасет по птице wide.xlsx
+++ b/Models/Птицы/Датасет по птице wide.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U121"/>
+  <dimension ref="A1:U128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7877,6 +7877,475 @@
         <v>565.34</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>8560.299999999999</v>
+      </c>
+      <c r="C122" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="D122" t="n">
+        <v>12023.33</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" t="n">
+        <v>6376.96</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J122" t="n">
+        <v>1983.67</v>
+      </c>
+      <c r="K122" t="n">
+        <v>972.64</v>
+      </c>
+      <c r="L122" t="n">
+        <v>1000.83</v>
+      </c>
+      <c r="M122" t="n">
+        <v>1481.59</v>
+      </c>
+      <c r="N122" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O122" t="n">
+        <v>508.83</v>
+      </c>
+      <c r="P122" t="n">
+        <v>1879.2</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>279.8</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
+        <v>319.17</v>
+      </c>
+      <c r="T122" t="n">
+        <v>414.0500000000001</v>
+      </c>
+      <c r="U122" t="n">
+        <v>810.6</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>12551.51</v>
+      </c>
+      <c r="C123" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="D123" t="n">
+        <v>10821.1</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" t="n">
+        <v>5574.809999999999</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>5.300000000000001</v>
+      </c>
+      <c r="J123" t="n">
+        <v>1817.65</v>
+      </c>
+      <c r="K123" t="n">
+        <v>1047.88</v>
+      </c>
+      <c r="L123" t="n">
+        <v>892.11</v>
+      </c>
+      <c r="M123" t="n">
+        <v>1377.83</v>
+      </c>
+      <c r="N123" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="O123" t="n">
+        <v>427.6</v>
+      </c>
+      <c r="P123" t="n">
+        <v>1683.5</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="n">
+        <v>252.85</v>
+      </c>
+      <c r="T123" t="n">
+        <v>496.82</v>
+      </c>
+      <c r="U123" t="n">
+        <v>641.64</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>12385.3</v>
+      </c>
+      <c r="C124" t="n">
+        <v>18</v>
+      </c>
+      <c r="D124" t="n">
+        <v>12752.96</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" t="n">
+        <v>6469.33</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J124" t="n">
+        <v>2596.07</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1179.17</v>
+      </c>
+      <c r="L124" t="n">
+        <v>877.7400000000001</v>
+      </c>
+      <c r="M124" t="n">
+        <v>1435.98</v>
+      </c>
+      <c r="N124" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O124" t="n">
+        <v>618.8</v>
+      </c>
+      <c r="P124" t="n">
+        <v>1821.7</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="n">
+        <v>234.53</v>
+      </c>
+      <c r="T124" t="n">
+        <v>705.66</v>
+      </c>
+      <c r="U124" t="n">
+        <v>802.3000000000001</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>13015.9</v>
+      </c>
+      <c r="C125" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="D125" t="n">
+        <v>13346.82</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>6486.09</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J125" t="n">
+        <v>1968.29</v>
+      </c>
+      <c r="K125" t="n">
+        <v>989.24</v>
+      </c>
+      <c r="L125" t="n">
+        <v>1046.8</v>
+      </c>
+      <c r="M125" t="n">
+        <v>1111.97</v>
+      </c>
+      <c r="N125" t="n">
+        <v>5.600000000000001</v>
+      </c>
+      <c r="O125" t="n">
+        <v>1039.88</v>
+      </c>
+      <c r="P125" t="n">
+        <v>2239.8</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>124.4</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>559.95</v>
+      </c>
+      <c r="T125" t="n">
+        <v>574.51</v>
+      </c>
+      <c r="U125" t="n">
+        <v>750.0700000000001</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>10609</v>
+      </c>
+      <c r="C126" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="D126" t="n">
+        <v>11619.21</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="n">
+        <v>6221.83</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J126" t="n">
+        <v>1939.64</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1101.94</v>
+      </c>
+      <c r="L126" t="n">
+        <v>920.1300000000001</v>
+      </c>
+      <c r="M126" t="n">
+        <v>1062.91</v>
+      </c>
+      <c r="N126" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O126" t="n">
+        <v>730.33</v>
+      </c>
+      <c r="P126" t="n">
+        <v>2224.7</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>280.2</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="n">
+        <v>564.4299999999999</v>
+      </c>
+      <c r="T126" t="n">
+        <v>682.0100000000001</v>
+      </c>
+      <c r="U126" t="n">
+        <v>754.3099999999999</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>10408.6</v>
+      </c>
+      <c r="C127" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="D127" t="n">
+        <v>10505.14</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" t="n">
+        <v>6069.309999999999</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J127" t="n">
+        <v>1631.96</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1008.55</v>
+      </c>
+      <c r="L127" t="n">
+        <v>1090.89</v>
+      </c>
+      <c r="M127" t="n">
+        <v>988.78</v>
+      </c>
+      <c r="N127" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="O127" t="n">
+        <v>876.72</v>
+      </c>
+      <c r="P127" t="n">
+        <v>1720.7</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>175.8</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="n">
+        <v>819.9599999999999</v>
+      </c>
+      <c r="T127" t="n">
+        <v>730.13</v>
+      </c>
+      <c r="U127" t="n">
+        <v>925.6700000000001</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>10639.7</v>
+      </c>
+      <c r="C128" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="D128" t="n">
+        <v>10844.25</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" t="n">
+        <v>6186.68</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>4</v>
+      </c>
+      <c r="J128" t="n">
+        <v>1759.46</v>
+      </c>
+      <c r="K128" t="n">
+        <v>912.9300000000001</v>
+      </c>
+      <c r="L128" t="n">
+        <v>866.5699999999999</v>
+      </c>
+      <c r="M128" t="n">
+        <v>1083.18</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O128" t="n">
+        <v>911.41</v>
+      </c>
+      <c r="P128" t="n">
+        <v>2036.8</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="R128" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="S128" t="n">
+        <v>914.2800000000001</v>
+      </c>
+      <c r="T128" t="n">
+        <v>978.5500000000001</v>
+      </c>
+      <c r="U128" t="n">
+        <v>627.5999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
